--- a/Expenses Form.xlsx
+++ b/Expenses Form.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://angusuk-my.sharepoint.com/personal/jonathan_mercado_nationalfoam_com/Documents/Expenses/auto/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://angusuk-my.sharepoint.com/personal/jonathan_mercado_nationalfoam_com/Documents/Expenses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{4FBDFD54-C8CF-4AE1-B4DB-67935017070C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D73238D-8DA1-4CE6-9982-D5406707F77F}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{4FBDFD54-C8CF-4AE1-B4DB-67935017070C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC7E6CE9-C2B9-4163-A0DC-D5C40F3DDF3A}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1500" windowWidth="25350" windowHeight="18360" xr2:uid="{D77FE8B0-0951-4BA3-AD45-825144AC6338}"/>
+    <workbookView xWindow="25470" yWindow="2340" windowWidth="24720" windowHeight="16050" xr2:uid="{D77FE8B0-0951-4BA3-AD45-825144AC6338}"/>
   </bookViews>
   <sheets>
     <sheet name="Page 1" sheetId="29" r:id="rId1"/>
+    <sheet name="Page 2" sheetId="30" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Page 1'!$J$4:$J$57</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Page 1'!$A$1:$J$57</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Page 2'!$A$1:$J$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="96">
   <si>
     <t>DATE</t>
   </si>
@@ -244,10 +246,53 @@
     <t>CURRENCY</t>
   </si>
   <si>
+    <t>National Foam, Inc</t>
+  </si>
+  <si>
     <t>TRAVEL EXPENSE REPORT</t>
   </si>
   <si>
+    <t>EXPENSE REPORT Page 2</t>
+  </si>
+  <si>
+    <t>ITEMIZED ENTERTAINMENT RECORD**</t>
+  </si>
+  <si>
+    <t>Customer / Client / Attendees</t>
+  </si>
+  <si>
+    <t>Persons Entertained</t>
+  </si>
+  <si>
+    <t>Business Relationship</t>
+  </si>
+  <si>
+    <t>Location, Type &amp; Purpose</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>FIELD SERVICE</t>
+  </si>
+  <si>
+    <t>Company Visited</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Service Performed</t>
+  </si>
+  <si>
+    <t>Details of Expenditure Marked Other**</t>
+  </si>
+  <si>
     <t>TOTAL EXPENSES PAYABLE TO EMPLOYEE</t>
+  </si>
+  <si>
+    <t>Unit 1 Code (Department)
+8085</t>
   </si>
   <si>
     <r>
@@ -281,7 +326,19 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Business Purpose of Expenses
+</t>
+  </si>
+  <si>
+    <t>Week Ending
+, 2019</t>
+  </si>
+  <si>
     <t>Company Car Fuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name
+</t>
   </si>
   <si>
     <t xml:space="preserve">BUSINESS MILES DRIVEN:  </t>
@@ -309,13 +366,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="mmmm\-yy"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="166" formatCode="mm/dd/yy;@"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -376,6 +434,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <u/>
       <sz val="9"/>
@@ -634,7 +698,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -809,13 +873,41 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -839,6 +931,30 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -847,7 +963,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -863,15 +979,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -899,15 +1015,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -923,28 +1039,72 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1473,56 +1633,56 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="E2" s="45" t="s">
-        <v>68</v>
+      <c r="E2" s="46" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
+        <v>94</v>
+      </c>
+      <c r="B4" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
-        <v>78</v>
+      <c r="A5" s="56" t="s">
+        <v>95</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="2"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="52"/>
+      <c r="E5" s="59"/>
       <c r="F5" s="6"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="58"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="71"/>
     </row>
     <row r="6" spans="1:10" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="78"/>
+      <c r="B6" s="64"/>
       <c r="C6" s="17" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="58" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="17" t="s">
@@ -1531,21 +1691,21 @@
       <c r="G6" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="51" t="s">
+      <c r="J6" s="58" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="78"/>
+      <c r="A7" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="64"/>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -1556,10 +1716,10 @@
       <c r="J7" s="16"/>
     </row>
     <row r="8" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="78" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="78"/>
+      <c r="A8" s="64" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="64"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
@@ -1570,10 +1730,10 @@
       <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="79" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="79"/>
+      <c r="A9" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="65"/>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
@@ -1585,31 +1745,31 @@
     </row>
     <row r="10" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B10" s="41">
         <v>0.7</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
       <c r="J10" s="16"/>
     </row>
     <row r="11" spans="1:10" s="8" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="74"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="76"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="62"/>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
@@ -1849,10 +2009,10 @@
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="71"/>
+      <c r="B24" s="84"/>
       <c r="C24" s="25">
         <f>SUM(C18:C23)</f>
         <v>0</v>
@@ -1926,7 +2086,7 @@
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B27" s="28" t="s">
         <v>44</v>
@@ -2003,10 +2163,10 @@
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="72" t="s">
+      <c r="A30" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="72"/>
+      <c r="B30" s="85"/>
       <c r="C30" s="25">
         <f>SUM(C25:C29)</f>
         <v>0</v>
@@ -2117,10 +2277,10 @@
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="B35" s="73"/>
+      <c r="B35" s="86"/>
       <c r="C35" s="25">
         <f>SUM(C31:C34)</f>
         <v>0</v>
@@ -2165,9 +2325,9 @@
       <c r="D36" s="19"/>
       <c r="E36" s="24"/>
       <c r="F36" s="24"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
       <c r="J36" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -2184,9 +2344,9 @@
       <c r="D37" s="19"/>
       <c r="E37" s="24"/>
       <c r="F37" s="24"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
       <c r="J37" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -2203,9 +2363,9 @@
       <c r="D38" s="19"/>
       <c r="E38" s="24"/>
       <c r="F38" s="24"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
       <c r="J38" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -2222,9 +2382,9 @@
       <c r="D39" s="19"/>
       <c r="E39" s="24"/>
       <c r="F39" s="24"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
       <c r="J39" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -2241,19 +2401,19 @@
       <c r="D40" s="19"/>
       <c r="E40" s="24"/>
       <c r="F40" s="24"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
       <c r="J40" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="72" t="s">
+      <c r="A41" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="72"/>
+      <c r="B41" s="85"/>
       <c r="C41" s="25">
         <f>SUM(C17,C24,C30,C35,C36:C40)-C17</f>
         <v>0</v>
@@ -2345,7 +2505,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="46" t="s">
+      <c r="A45" s="50" t="s">
         <v>60</v>
       </c>
       <c r="B45" s="21"/>
@@ -2459,7 +2619,7 @@
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="46" t="s">
+      <c r="A50" s="50" t="s">
         <v>65</v>
       </c>
       <c r="B50" s="21"/>
@@ -2509,10 +2669,10 @@
       <c r="J51" s="19"/>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="72" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52" s="72"/>
+      <c r="A52" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="85"/>
       <c r="C52" s="25">
         <f>SUM(C41,C45,C50)</f>
         <v>0</v>
@@ -2565,16 +2725,16 @@
       <c r="D54" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E54" s="62" t="s">
+      <c r="E54" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="63"/>
-      <c r="G54" s="63"/>
-      <c r="H54" s="64"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="77"/>
       <c r="I54" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="J54" s="59">
+      <c r="J54" s="72">
         <f>J52</f>
         <v>0</v>
       </c>
@@ -2583,15 +2743,15 @@
       <c r="A55" s="32"/>
       <c r="B55" s="33"/>
       <c r="C55" s="34"/>
-      <c r="D55" s="50"/>
-      <c r="E55" s="65"/>
-      <c r="F55" s="66"/>
-      <c r="G55" s="66"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="68" t="s">
+      <c r="D55" s="57"/>
+      <c r="E55" s="78"/>
+      <c r="F55" s="79"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="80"/>
+      <c r="I55" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="J55" s="60"/>
+      <c r="J55" s="73"/>
     </row>
     <row r="56" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="29" t="s">
@@ -2610,8 +2770,8 @@
       <c r="H56" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I56" s="69"/>
-      <c r="J56" s="60"/>
+      <c r="I56" s="82"/>
+      <c r="J56" s="73"/>
     </row>
     <row r="57" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="32"/>
@@ -2622,12 +2782,11 @@
       <c r="F57" s="34"/>
       <c r="G57" s="34"/>
       <c r="H57" s="38"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="61"/>
+      <c r="I57" s="83"/>
+      <c r="J57" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A9:B9"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="F4:J4"/>
@@ -2644,6 +2803,7 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="60" orientation="landscape"/>
@@ -2651,10 +2811,895 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323E83F1-535C-45C1-831C-C1F563843341}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:J57"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30" style="45" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="20.42578125" style="45" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="20.42578125" style="45" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="45"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="89" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="90"/>
+      <c r="C3" s="89" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="90"/>
+      <c r="E3" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="90"/>
+      <c r="G3" s="89" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="90"/>
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="91"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="92"/>
+    </row>
+    <row r="5" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="95"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="97"/>
+    </row>
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="97"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="87"/>
+      <c r="J7" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="51"/>
+    </row>
+    <row r="9" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="88"/>
+      <c r="J9" s="51"/>
+    </row>
+    <row r="10" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="51"/>
+    </row>
+    <row r="11" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="51"/>
+    </row>
+    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="51"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="11"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="11"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="11"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="11"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="11"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="11"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="11"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="11"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="11"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="11"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="87"/>
+      <c r="J20" s="11"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="11"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="87"/>
+      <c r="J21" s="11"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="11"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="87"/>
+      <c r="I22" s="87"/>
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="11"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
+      <c r="F23" s="87"/>
+      <c r="G23" s="87"/>
+      <c r="H23" s="87"/>
+      <c r="I23" s="87"/>
+      <c r="J23" s="11"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="11"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="11"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="11"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="11"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="11"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="11"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="11"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="87"/>
+      <c r="H27" s="87"/>
+      <c r="I27" s="87"/>
+      <c r="J27" s="11"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="11"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="87"/>
+      <c r="J28" s="11"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="11"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="87"/>
+      <c r="H29" s="87"/>
+      <c r="I29" s="87"/>
+      <c r="J29" s="11"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="11"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="87"/>
+      <c r="I30" s="87"/>
+      <c r="J30" s="11"/>
+    </row>
+    <row r="31" spans="1:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="95"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="97"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="95" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="96"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="96"/>
+      <c r="H32" s="96"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="97"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="95" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="96"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="95" t="s">
+        <v>79</v>
+      </c>
+      <c r="G33" s="97"/>
+      <c r="H33" s="95" t="s">
+        <v>80</v>
+      </c>
+      <c r="I33" s="96"/>
+      <c r="J33" s="97"/>
+    </row>
+    <row r="34" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="11"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="99"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="97"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="96"/>
+      <c r="J34" s="97"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="11"/>
+      <c r="B35" s="95"/>
+      <c r="C35" s="96"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="95"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="95"/>
+      <c r="I35" s="96"/>
+      <c r="J35" s="97"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="11"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="96"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="97"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="97"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="97"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="11"/>
+      <c r="B37" s="95"/>
+      <c r="C37" s="96"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="97"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="97"/>
+      <c r="H37" s="95"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="97"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="11"/>
+      <c r="B38" s="95"/>
+      <c r="C38" s="96"/>
+      <c r="D38" s="96"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="95"/>
+      <c r="G38" s="97"/>
+      <c r="H38" s="95"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="97"/>
+    </row>
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="11"/>
+      <c r="B39" s="95"/>
+      <c r="C39" s="96"/>
+      <c r="D39" s="96"/>
+      <c r="E39" s="97"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="97"/>
+      <c r="H39" s="95"/>
+      <c r="I39" s="96"/>
+      <c r="J39" s="97"/>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="11"/>
+      <c r="B40" s="95"/>
+      <c r="C40" s="96"/>
+      <c r="D40" s="96"/>
+      <c r="E40" s="97"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="97"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="97"/>
+    </row>
+    <row r="41" spans="1:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="87"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="87"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="87"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="87"/>
+      <c r="H41" s="87"/>
+      <c r="I41" s="87"/>
+      <c r="J41" s="87"/>
+    </row>
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" s="95" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="96"/>
+      <c r="D42" s="96"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="96"/>
+      <c r="H42" s="96"/>
+      <c r="I42" s="97"/>
+      <c r="J42" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="53"/>
+      <c r="B43" s="101"/>
+      <c r="C43" s="102"/>
+      <c r="D43" s="102"/>
+      <c r="E43" s="102"/>
+      <c r="F43" s="102"/>
+      <c r="G43" s="102"/>
+      <c r="H43" s="102"/>
+      <c r="I43" s="103"/>
+      <c r="J43" s="51"/>
+    </row>
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="11"/>
+      <c r="B44" s="95"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
+      <c r="F44" s="96"/>
+      <c r="G44" s="96"/>
+      <c r="H44" s="96"/>
+      <c r="I44" s="97"/>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="11"/>
+      <c r="B45" s="95"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
+      <c r="F45" s="96"/>
+      <c r="G45" s="96"/>
+      <c r="H45" s="96"/>
+      <c r="I45" s="97"/>
+      <c r="J45" s="11"/>
+    </row>
+    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="11"/>
+      <c r="B46" s="95"/>
+      <c r="C46" s="96"/>
+      <c r="D46" s="96"/>
+      <c r="E46" s="96"/>
+      <c r="F46" s="96"/>
+      <c r="G46" s="96"/>
+      <c r="H46" s="96"/>
+      <c r="I46" s="97"/>
+      <c r="J46" s="11"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="11"/>
+      <c r="B47" s="95"/>
+      <c r="C47" s="96"/>
+      <c r="D47" s="96"/>
+      <c r="E47" s="96"/>
+      <c r="F47" s="96"/>
+      <c r="G47" s="96"/>
+      <c r="H47" s="96"/>
+      <c r="I47" s="97"/>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="11"/>
+      <c r="B48" s="95"/>
+      <c r="C48" s="96"/>
+      <c r="D48" s="96"/>
+      <c r="E48" s="96"/>
+      <c r="F48" s="96"/>
+      <c r="G48" s="96"/>
+      <c r="H48" s="96"/>
+      <c r="I48" s="97"/>
+      <c r="J48" s="11"/>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="11"/>
+      <c r="B49" s="95"/>
+      <c r="C49" s="96"/>
+      <c r="D49" s="96"/>
+      <c r="E49" s="96"/>
+      <c r="F49" s="96"/>
+      <c r="G49" s="96"/>
+      <c r="H49" s="96"/>
+      <c r="I49" s="97"/>
+      <c r="J49" s="11"/>
+    </row>
+    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="11"/>
+      <c r="B50" s="95"/>
+      <c r="C50" s="96"/>
+      <c r="D50" s="96"/>
+      <c r="E50" s="96"/>
+      <c r="F50" s="96"/>
+      <c r="G50" s="96"/>
+      <c r="H50" s="96"/>
+      <c r="I50" s="97"/>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="11"/>
+      <c r="B51" s="95"/>
+      <c r="C51" s="96"/>
+      <c r="D51" s="96"/>
+      <c r="E51" s="96"/>
+      <c r="F51" s="96"/>
+      <c r="G51" s="96"/>
+      <c r="H51" s="96"/>
+      <c r="I51" s="97"/>
+      <c r="J51" s="11"/>
+    </row>
+    <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="11"/>
+      <c r="B52" s="95"/>
+      <c r="C52" s="96"/>
+      <c r="D52" s="96"/>
+      <c r="E52" s="96"/>
+      <c r="F52" s="96"/>
+      <c r="G52" s="96"/>
+      <c r="H52" s="96"/>
+      <c r="I52" s="97"/>
+      <c r="J52" s="11"/>
+    </row>
+    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="11"/>
+      <c r="B53" s="95"/>
+      <c r="C53" s="96"/>
+      <c r="D53" s="96"/>
+      <c r="E53" s="96"/>
+      <c r="F53" s="96"/>
+      <c r="G53" s="96"/>
+      <c r="H53" s="96"/>
+      <c r="I53" s="97"/>
+      <c r="J53" s="11"/>
+    </row>
+    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="11"/>
+      <c r="B54" s="95"/>
+      <c r="C54" s="96"/>
+      <c r="D54" s="96"/>
+      <c r="E54" s="96"/>
+      <c r="F54" s="96"/>
+      <c r="G54" s="96"/>
+      <c r="H54" s="96"/>
+      <c r="I54" s="97"/>
+      <c r="J54" s="11"/>
+    </row>
+    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="11"/>
+      <c r="B55" s="95"/>
+      <c r="C55" s="96"/>
+      <c r="D55" s="96"/>
+      <c r="E55" s="96"/>
+      <c r="F55" s="96"/>
+      <c r="G55" s="96"/>
+      <c r="H55" s="96"/>
+      <c r="I55" s="97"/>
+      <c r="J55" s="11"/>
+    </row>
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="11"/>
+      <c r="B56" s="95"/>
+      <c r="C56" s="96"/>
+      <c r="D56" s="96"/>
+      <c r="E56" s="96"/>
+      <c r="F56" s="96"/>
+      <c r="G56" s="96"/>
+      <c r="H56" s="96"/>
+      <c r="I56" s="97"/>
+      <c r="J56" s="11"/>
+    </row>
+    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="11"/>
+      <c r="B57" s="95"/>
+      <c r="C57" s="96"/>
+      <c r="D57" s="96"/>
+      <c r="E57" s="96"/>
+      <c r="F57" s="96"/>
+      <c r="G57" s="96"/>
+      <c r="H57" s="96"/>
+      <c r="I57" s="97"/>
+      <c r="J57" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="145">
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="G3:J4"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" orientation="landscape"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2887,19 +3932,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{208F9D4A-BA73-4BBA-946D-C19CFC18DBC7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A345859F-55D6-4262-B8E7-7E8C8C7CAD50}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2924,9 +3965,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A345859F-55D6-4262-B8E7-7E8C8C7CAD50}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{208F9D4A-BA73-4BBA-946D-C19CFC18DBC7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Expenses Form.xlsx
+++ b/Expenses Form.xlsx
@@ -474,7 +474,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -483,16 +483,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -504,7 +581,61 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -531,29 +662,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -567,8 +676,12 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -577,9 +690,7 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -590,73 +701,8 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -669,36 +715,27 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1105,6 +1142,313 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="39" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="2" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1638,7 +1982,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="104" t="s">
         <v>94</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -1648,1142 +1992,1142 @@
       <c r="D4" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="66"/>
+      <c r="E4" s="105"/>
       <c r="F4" s="67" t="s">
         <v>84</v>
       </c>
       <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="106"/>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="107" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="71"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="118"/>
+      <c r="C6" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="E6" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="58" t="s">
+      <c r="H6" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="58" t="s">
+      <c r="I6" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="58" t="s">
+      <c r="J6" s="120" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="16"/>
+      <c r="A7" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="118"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="121"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="122"/>
     </row>
     <row r="8" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="118" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="16"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="123" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="16"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="124" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="125">
         <v>0.7</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="16"/>
+      <c r="C10" s="126"/>
+      <c r="D10" s="126"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" s="8" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="60"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="62"/>
+      <c r="A11" s="127"/>
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="129"/>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19">
+      <c r="B12" s="131"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="132">
         <f t="shared" ref="J12:J17" si="0">SUM(C12:I12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19">
+      <c r="B13" s="130"/>
+      <c r="C13" s="132"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19">
+      <c r="B14" s="130"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="132">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19">
+      <c r="B15" s="130"/>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19">
+      <c r="B16" s="130"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="132">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="26">
+      <c r="B17" s="133"/>
+      <c r="C17" s="134">
         <f>SUM(C12:C16)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="134">
         <f t="shared" ref="D17:I17" si="1">SUM(D12:D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="134">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="134">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="134">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="134">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="134">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="26">
+      <c r="J17" s="134">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="136" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24">
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="137"/>
+      <c r="H18" s="137"/>
+      <c r="I18" s="137"/>
+      <c r="J18" s="137">
         <f t="shared" ref="J18:J23" si="2">SUM(C18:I18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="136" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24">
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
+      <c r="H19" s="137"/>
+      <c r="I19" s="137"/>
+      <c r="J19" s="137">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24">
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
+      <c r="H20" s="137"/>
+      <c r="I20" s="137"/>
+      <c r="J20" s="137">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="136" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24">
+      <c r="C21" s="137"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="137"/>
+      <c r="I21" s="137"/>
+      <c r="J21" s="137">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24">
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="137">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="135" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24">
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="137"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="137"/>
+      <c r="I23" s="137"/>
+      <c r="J23" s="137">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="84" t="s">
+      <c r="A24" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="84"/>
-      <c r="C24" s="25">
+      <c r="B24" s="138"/>
+      <c r="C24" s="139">
         <f>SUM(C18:C23)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="139">
         <f t="shared" ref="D24:J24" si="3">SUM(D18:D23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="139">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="139">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="139">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H24" s="25">
+      <c r="H24" s="139">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I24" s="25">
+      <c r="I24" s="139">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="25">
+      <c r="J24" s="139">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24">
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
+      <c r="H25" s="137"/>
+      <c r="I25" s="137"/>
+      <c r="J25" s="137">
         <f>SUM(C25:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="140" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24">
+      <c r="C26" s="137"/>
+      <c r="D26" s="137"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="137"/>
+      <c r="G26" s="137"/>
+      <c r="H26" s="137"/>
+      <c r="I26" s="137"/>
+      <c r="J26" s="137">
         <f>SUM(C26:I26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="131" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24">
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="137"/>
+      <c r="I27" s="137"/>
+      <c r="J27" s="137">
         <f>SUM(C27:I27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24">
+      <c r="C28" s="137"/>
+      <c r="D28" s="137"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="137"/>
+      <c r="G28" s="137"/>
+      <c r="H28" s="137"/>
+      <c r="I28" s="137"/>
+      <c r="J28" s="137">
         <f>SUM(C28:I28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="137">
         <f>B10*C10</f>
         <v>0</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="137">
         <f>B10*D10</f>
         <v>0</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="137">
         <f>B10*E10</f>
         <v>0</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="137">
         <f>B10*F10</f>
         <v>0</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="137">
         <f>B10*G10</f>
         <v>0</v>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="137">
         <f>B10*H10</f>
         <v>0</v>
       </c>
-      <c r="I29" s="24">
+      <c r="I29" s="137">
         <f>B10*I10</f>
         <v>0</v>
       </c>
-      <c r="J29" s="24">
+      <c r="J29" s="137">
         <f>SUM(C29:I29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="85" t="s">
+      <c r="A30" s="141" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="85"/>
-      <c r="C30" s="25">
+      <c r="B30" s="141"/>
+      <c r="C30" s="139">
         <f>SUM(C25:C29)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="139">
         <f t="shared" ref="D30:J30" si="4">SUM(D25:D29)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="139">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="139">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="139">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="139">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I30" s="25">
+      <c r="I30" s="139">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="25">
+      <c r="J30" s="139">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="140" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="19">
+      <c r="C31" s="137"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="137"/>
+      <c r="F31" s="137"/>
+      <c r="G31" s="137"/>
+      <c r="H31" s="137"/>
+      <c r="I31" s="137"/>
+      <c r="J31" s="132">
         <f>SUM(C31:I31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="19">
+      <c r="C32" s="137"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="137"/>
+      <c r="H32" s="137"/>
+      <c r="I32" s="137"/>
+      <c r="J32" s="132">
         <f t="shared" ref="J32:J41" si="5">SUM(C32:I32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="140" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="131" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="19">
+      <c r="C33" s="137"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="137"/>
+      <c r="F33" s="137"/>
+      <c r="G33" s="137"/>
+      <c r="H33" s="137"/>
+      <c r="I33" s="137"/>
+      <c r="J33" s="132">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="19">
+      <c r="C34" s="137"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="137"/>
+      <c r="F34" s="137"/>
+      <c r="G34" s="137"/>
+      <c r="H34" s="137"/>
+      <c r="I34" s="137"/>
+      <c r="J34" s="132">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="86" t="s">
+      <c r="A35" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="B35" s="86"/>
-      <c r="C35" s="25">
+      <c r="B35" s="142"/>
+      <c r="C35" s="139">
         <f>SUM(C31:C34)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="139">
         <f t="shared" ref="D35:I35" si="6">SUM(D31:D34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="139">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="139">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="139">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H35" s="25">
+      <c r="H35" s="139">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I35" s="25">
+      <c r="I35" s="139">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J35" s="26">
+      <c r="J35" s="134">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="140" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="24"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="19">
+      <c r="C36" s="137"/>
+      <c r="D36" s="132"/>
+      <c r="E36" s="137"/>
+      <c r="F36" s="137"/>
+      <c r="G36" s="143"/>
+      <c r="H36" s="143"/>
+      <c r="I36" s="143"/>
+      <c r="J36" s="132">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="131" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="19">
+      <c r="C37" s="137"/>
+      <c r="D37" s="132"/>
+      <c r="E37" s="137"/>
+      <c r="F37" s="137"/>
+      <c r="G37" s="143"/>
+      <c r="H37" s="143"/>
+      <c r="I37" s="143"/>
+      <c r="J37" s="132">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="131" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="19">
+      <c r="C38" s="137"/>
+      <c r="D38" s="132"/>
+      <c r="E38" s="137"/>
+      <c r="F38" s="137"/>
+      <c r="G38" s="143"/>
+      <c r="H38" s="143"/>
+      <c r="I38" s="143"/>
+      <c r="J38" s="132">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="131" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="19">
+      <c r="C39" s="137"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="137"/>
+      <c r="G39" s="143"/>
+      <c r="H39" s="143"/>
+      <c r="I39" s="143"/>
+      <c r="J39" s="132">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="24"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="19">
+      <c r="C40" s="137"/>
+      <c r="D40" s="132"/>
+      <c r="E40" s="137"/>
+      <c r="F40" s="137"/>
+      <c r="G40" s="143"/>
+      <c r="H40" s="143"/>
+      <c r="I40" s="143"/>
+      <c r="J40" s="132">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="85" t="s">
+      <c r="A41" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="85"/>
-      <c r="C41" s="25">
+      <c r="B41" s="141"/>
+      <c r="C41" s="139">
         <f>SUM(C17,C24,C30,C35,C36:C40)-C17</f>
         <v>0</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="139">
         <f t="shared" ref="D41:I41" si="7">SUM(D17,D24,D30,D35,D36:D40)-D17</f>
         <v>0</v>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="139">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F41" s="25">
+      <c r="F41" s="139">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G41" s="25">
+      <c r="G41" s="139">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H41" s="25">
+      <c r="H41" s="139">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I41" s="25">
+      <c r="I41" s="139">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J41" s="26">
+      <c r="J41" s="134">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="19">
+      <c r="C42" s="137"/>
+      <c r="D42" s="137"/>
+      <c r="E42" s="137"/>
+      <c r="F42" s="137"/>
+      <c r="G42" s="137"/>
+      <c r="H42" s="137"/>
+      <c r="I42" s="137"/>
+      <c r="J42" s="132">
         <f>SUM(C42:I42)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="19">
+      <c r="C43" s="137"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="137"/>
+      <c r="G43" s="137"/>
+      <c r="H43" s="137"/>
+      <c r="I43" s="137"/>
+      <c r="J43" s="132">
         <f t="shared" ref="J43:J50" si="8">SUM(C43:I43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="140" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="19">
+      <c r="C44" s="137"/>
+      <c r="D44" s="137"/>
+      <c r="E44" s="137"/>
+      <c r="F44" s="137"/>
+      <c r="G44" s="137"/>
+      <c r="H44" s="137"/>
+      <c r="I44" s="137"/>
+      <c r="J44" s="132">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="50" t="s">
+      <c r="A45" s="146" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="21"/>
-      <c r="C45" s="25">
+      <c r="B45" s="140"/>
+      <c r="C45" s="139">
         <f>SUM(C42:C44)</f>
         <v>0</v>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="139">
         <f t="shared" ref="D45:I45" si="9">SUM(D42:D44)</f>
         <v>0</v>
       </c>
-      <c r="E45" s="25">
+      <c r="E45" s="139">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F45" s="25">
+      <c r="F45" s="139">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G45" s="25">
+      <c r="G45" s="139">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H45" s="25">
+      <c r="H45" s="139">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I45" s="25">
+      <c r="I45" s="139">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J45" s="26">
+      <c r="J45" s="134">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="140" t="s">
         <v>61</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="19">
+      <c r="C46" s="137"/>
+      <c r="D46" s="137"/>
+      <c r="E46" s="137"/>
+      <c r="F46" s="137"/>
+      <c r="G46" s="137"/>
+      <c r="H46" s="137"/>
+      <c r="I46" s="137"/>
+      <c r="J46" s="132">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="19">
+      <c r="C47" s="137"/>
+      <c r="D47" s="137"/>
+      <c r="E47" s="137"/>
+      <c r="F47" s="137"/>
+      <c r="G47" s="137"/>
+      <c r="H47" s="137"/>
+      <c r="I47" s="137"/>
+      <c r="J47" s="132">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="140" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="19">
+      <c r="C48" s="137"/>
+      <c r="D48" s="137"/>
+      <c r="E48" s="137"/>
+      <c r="F48" s="137"/>
+      <c r="G48" s="137"/>
+      <c r="H48" s="137"/>
+      <c r="I48" s="137"/>
+      <c r="J48" s="132">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="19">
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="137"/>
+      <c r="F49" s="137"/>
+      <c r="G49" s="137"/>
+      <c r="H49" s="137"/>
+      <c r="I49" s="137"/>
+      <c r="J49" s="132">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="50" t="s">
+      <c r="A50" s="146" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="21"/>
-      <c r="C50" s="25">
+      <c r="B50" s="140"/>
+      <c r="C50" s="139">
         <f>SUM(C46:C49)</f>
         <v>0</v>
       </c>
-      <c r="D50" s="25">
+      <c r="D50" s="139">
         <f t="shared" ref="D50:I50" si="10">SUM(D46:D49)</f>
         <v>0</v>
       </c>
-      <c r="E50" s="25">
+      <c r="E50" s="139">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F50" s="25">
+      <c r="F50" s="139">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G50" s="25">
+      <c r="G50" s="139">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H50" s="25">
+      <c r="H50" s="139">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I50" s="25">
+      <c r="I50" s="139">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J50" s="26">
+      <c r="J50" s="134">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="42"/>
-      <c r="B51" s="43"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="24"/>
-      <c r="J51" s="19"/>
+      <c r="A51" s="147"/>
+      <c r="B51" s="148"/>
+      <c r="C51" s="137"/>
+      <c r="D51" s="137"/>
+      <c r="E51" s="137"/>
+      <c r="F51" s="137"/>
+      <c r="G51" s="137"/>
+      <c r="H51" s="137"/>
+      <c r="I51" s="137"/>
+      <c r="J51" s="132"/>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="141" t="s">
         <v>82</v>
       </c>
-      <c r="B52" s="85"/>
-      <c r="C52" s="25">
+      <c r="B52" s="141"/>
+      <c r="C52" s="139">
         <f>SUM(C41,C45,C50)</f>
         <v>0</v>
       </c>
-      <c r="D52" s="25">
+      <c r="D52" s="139">
         <f t="shared" ref="D52:I52" si="11">SUM(D41,D45,D50)</f>
         <v>0</v>
       </c>
-      <c r="E52" s="25">
+      <c r="E52" s="139">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F52" s="25">
+      <c r="F52" s="139">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G52" s="25">
+      <c r="G52" s="139">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H52" s="25">
+      <c r="H52" s="139">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I52" s="25">
+      <c r="I52" s="139">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J52" s="25">
+      <c r="J52" s="139">
         <f>SUM(C52:I52)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C53" s="9"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="13"/>
+      <c r="C53" s="149"/>
+      <c r="D53" s="150"/>
+      <c r="E53" s="149"/>
+      <c r="F53" s="149"/>
+      <c r="G53" s="150"/>
+      <c r="H53" s="150"/>
+      <c r="I53" s="150"/>
+      <c r="J53" s="151"/>
     </row>
     <row r="54" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="29" t="s">
+      <c r="A54" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="30"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="39" t="s">
+      <c r="B54" s="153"/>
+      <c r="C54" s="154"/>
+      <c r="D54" s="155" t="s">
         <v>1</v>
       </c>
-      <c r="E54" s="75" t="s">
+      <c r="E54" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="76"/>
-      <c r="G54" s="76"/>
-      <c r="H54" s="77"/>
-      <c r="I54" s="44" t="s">
+      <c r="F54" s="157"/>
+      <c r="G54" s="157"/>
+      <c r="H54" s="158"/>
+      <c r="I54" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="J54" s="72">
+      <c r="J54" s="160">
         <f>J52</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="32"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="34"/>
-      <c r="D55" s="57"/>
-      <c r="E55" s="78"/>
-      <c r="F55" s="79"/>
-      <c r="G55" s="79"/>
-      <c r="H55" s="80"/>
-      <c r="I55" s="81" t="s">
+      <c r="A55" s="161"/>
+      <c r="B55" s="162"/>
+      <c r="C55" s="163"/>
+      <c r="D55" s="164"/>
+      <c r="E55" s="165"/>
+      <c r="F55" s="166"/>
+      <c r="G55" s="166"/>
+      <c r="H55" s="167"/>
+      <c r="I55" s="168" t="s">
         <v>66</v>
       </c>
-      <c r="J55" s="73"/>
+      <c r="J55" s="169"/>
     </row>
     <row r="56" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="B56" s="30"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="36" t="s">
+      <c r="B56" s="153"/>
+      <c r="C56" s="154"/>
+      <c r="D56" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="E56" s="40" t="s">
+      <c r="E56" s="171" t="s">
         <v>54</v>
       </c>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="36" t="s">
+      <c r="F56" s="172"/>
+      <c r="G56" s="173"/>
+      <c r="H56" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="I56" s="82"/>
-      <c r="J56" s="73"/>
+      <c r="I56" s="174"/>
+      <c r="J56" s="169"/>
     </row>
     <row r="57" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="32"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="34"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="34"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="83"/>
-      <c r="J57" s="74"/>
+      <c r="A57" s="161"/>
+      <c r="B57" s="162"/>
+      <c r="C57" s="163"/>
+      <c r="D57" s="175"/>
+      <c r="E57" s="176"/>
+      <c r="F57" s="177"/>
+      <c r="G57" s="163"/>
+      <c r="H57" s="178"/>
+      <c r="I57" s="179"/>
+      <c r="J57" s="180"/>
     </row>
   </sheetData>
   <mergeCells count="17">

--- a/Expenses Form.xlsx
+++ b/Expenses Form.xlsx
@@ -483,9 +483,15 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -495,9 +501,25 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -507,7 +529,140 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
@@ -528,48 +683,11 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -581,149 +699,21 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -735,7 +725,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1144,174 +1134,154 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf applyBorder="1" numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf applyBorder="1" numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf applyBorder="1" numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf applyBorder="1" numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf applyBorder="1" numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf applyBorder="1" numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1319,19 +1289,11 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf applyBorder="1" numFmtId="39" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1343,111 +1305,95 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="2" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf applyBorder="1" numFmtId="2" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1982,7 +1928,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="14" t="s">
         <v>94</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -1992,1142 +1938,1142 @@
       <c r="D4" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="105"/>
+      <c r="E4" s="66"/>
       <c r="F4" s="67" t="s">
         <v>84</v>
       </c>
       <c r="G4" s="68"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="106"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="116"/>
+      <c r="B5" s="105"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="112"/>
     </row>
     <row r="6" spans="1:10" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="117" t="s">
+      <c r="A6" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="119" t="s">
+      <c r="B6" s="114"/>
+      <c r="C6" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="D6" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="120" t="s">
+      <c r="E6" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="119" t="s">
+      <c r="F6" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="119" t="s">
+      <c r="G6" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="120" t="s">
+      <c r="H6" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="120" t="s">
+      <c r="I6" s="116" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="120" t="s">
+      <c r="J6" s="116" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="122"/>
+      <c r="A7" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="114"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="118"/>
     </row>
     <row r="8" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="114" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="B8" s="114"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="123" t="s">
+      <c r="A9" s="119" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="123"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="124" t="s">
+      <c r="A10" s="120" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="125">
+      <c r="B10" s="121">
         <v>0.7</v>
       </c>
-      <c r="C10" s="126"/>
-      <c r="D10" s="126"/>
-      <c r="E10" s="126"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="126"/>
-      <c r="I10" s="126"/>
-      <c r="J10" s="122"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="122"/>
+      <c r="F10" s="122"/>
+      <c r="G10" s="122"/>
+      <c r="H10" s="122"/>
+      <c r="I10" s="122"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" s="8" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="127"/>
-      <c r="B11" s="128"/>
-      <c r="C11" s="128"/>
-      <c r="D11" s="128"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="128"/>
-      <c r="J11" s="129"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="123"/>
+      <c r="F11" s="123"/>
+      <c r="G11" s="123"/>
+      <c r="H11" s="123"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="124"/>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="130" t="s">
+      <c r="A12" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="131"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
-      <c r="F12" s="132"/>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="132">
+      <c r="B12" s="126"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127">
         <f t="shared" ref="J12:J17" si="0">SUM(C12:I12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="130" t="s">
+      <c r="A13" s="125" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="130"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="132">
+      <c r="B13" s="125"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="127">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="130" t="s">
+      <c r="A14" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="130"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="132">
+      <c r="B14" s="125"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="130" t="s">
+      <c r="A15" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="130"/>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132">
+      <c r="B15" s="125"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="127"/>
+      <c r="I15" s="127"/>
+      <c r="J15" s="127">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="130" t="s">
+      <c r="A16" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="130"/>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="132"/>
-      <c r="G16" s="132"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="132"/>
-      <c r="J16" s="132">
+      <c r="B16" s="125"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="127"/>
+      <c r="J16" s="127">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="133" t="s">
+      <c r="A17" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="134">
+      <c r="B17" s="128"/>
+      <c r="C17" s="129">
         <f>SUM(C12:C16)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="134">
+      <c r="D17" s="129">
         <f t="shared" ref="D17:I17" si="1">SUM(D12:D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="134">
+      <c r="E17" s="129">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F17" s="134">
+      <c r="F17" s="129">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="134">
+      <c r="G17" s="129">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H17" s="134">
+      <c r="H17" s="129">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I17" s="134">
+      <c r="I17" s="129">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="134">
+      <c r="J17" s="129">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="135" t="s">
+      <c r="A18" s="130" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="136" t="s">
+      <c r="B18" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="137"/>
-      <c r="D18" s="137"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="137"/>
-      <c r="G18" s="137"/>
-      <c r="H18" s="137"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="137">
+      <c r="C18" s="132"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="132"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="132">
         <f t="shared" ref="J18:J23" si="2">SUM(C18:I18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="135" t="s">
+      <c r="A19" s="130" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="136" t="s">
+      <c r="B19" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="137"/>
-      <c r="D19" s="137"/>
-      <c r="E19" s="137"/>
-      <c r="F19" s="137"/>
-      <c r="G19" s="137"/>
-      <c r="H19" s="137"/>
-      <c r="I19" s="137"/>
-      <c r="J19" s="137">
+      <c r="C19" s="132"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="132"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="132"/>
+      <c r="J19" s="132">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="135" t="s">
+      <c r="A20" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="136" t="s">
+      <c r="B20" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="137"/>
-      <c r="D20" s="137"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="137"/>
-      <c r="G20" s="137"/>
-      <c r="H20" s="137"/>
-      <c r="I20" s="137"/>
-      <c r="J20" s="137">
+      <c r="C20" s="132"/>
+      <c r="D20" s="132"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="132"/>
+      <c r="G20" s="132"/>
+      <c r="H20" s="132"/>
+      <c r="I20" s="132"/>
+      <c r="J20" s="132">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="135" t="s">
+      <c r="A21" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="136" t="s">
+      <c r="B21" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="137"/>
-      <c r="D21" s="137"/>
-      <c r="E21" s="137"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="137"/>
-      <c r="H21" s="137"/>
-      <c r="I21" s="137"/>
-      <c r="J21" s="137">
+      <c r="C21" s="132"/>
+      <c r="D21" s="132"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="132"/>
+      <c r="J21" s="132">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="135" t="s">
+      <c r="A22" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="136" t="s">
+      <c r="B22" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="137"/>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="137"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="137">
+      <c r="C22" s="132"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="132"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="132"/>
+      <c r="J22" s="132">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="135" t="s">
+      <c r="A23" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="136" t="s">
+      <c r="B23" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="137"/>
-      <c r="D23" s="137"/>
-      <c r="E23" s="137"/>
-      <c r="F23" s="137"/>
-      <c r="G23" s="137"/>
-      <c r="H23" s="137"/>
-      <c r="I23" s="137"/>
-      <c r="J23" s="137">
+      <c r="C23" s="132"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="132"/>
+      <c r="J23" s="132">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="138" t="s">
+      <c r="A24" s="133" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="138"/>
-      <c r="C24" s="139">
+      <c r="B24" s="133"/>
+      <c r="C24" s="134">
         <f>SUM(C18:C23)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="139">
+      <c r="D24" s="134">
         <f t="shared" ref="D24:J24" si="3">SUM(D18:D23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="139">
+      <c r="E24" s="134">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F24" s="139">
+      <c r="F24" s="134">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G24" s="139">
+      <c r="G24" s="134">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H24" s="139">
+      <c r="H24" s="134">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I24" s="139">
+      <c r="I24" s="134">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="139">
+      <c r="J24" s="134">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="140" t="s">
+      <c r="A25" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="131" t="s">
+      <c r="B25" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="137"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="137"/>
-      <c r="H25" s="137"/>
-      <c r="I25" s="137"/>
-      <c r="J25" s="137">
+      <c r="C25" s="132"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="132"/>
+      <c r="J25" s="132">
         <f>SUM(C25:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="140" t="s">
+      <c r="A26" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="131" t="s">
+      <c r="B26" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="137"/>
-      <c r="D26" s="137"/>
-      <c r="E26" s="137"/>
-      <c r="F26" s="137"/>
-      <c r="G26" s="137"/>
-      <c r="H26" s="137"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="137">
+      <c r="C26" s="132"/>
+      <c r="D26" s="132"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="132"/>
+      <c r="H26" s="132"/>
+      <c r="I26" s="132"/>
+      <c r="J26" s="132">
         <f>SUM(C26:I26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="140" t="s">
+      <c r="A27" s="135" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="131" t="s">
+      <c r="B27" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="137"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="137"/>
-      <c r="F27" s="137"/>
-      <c r="G27" s="137"/>
-      <c r="H27" s="137"/>
-      <c r="I27" s="137"/>
-      <c r="J27" s="137">
+      <c r="C27" s="132"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="132">
         <f>SUM(C27:I27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="140" t="s">
+      <c r="A28" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="131" t="s">
+      <c r="B28" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="137"/>
-      <c r="D28" s="137"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="137"/>
-      <c r="G28" s="137"/>
-      <c r="H28" s="137"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="137">
+      <c r="C28" s="132"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="132"/>
+      <c r="J28" s="132">
         <f>SUM(C28:I28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="140" t="s">
+      <c r="A29" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="131" t="s">
+      <c r="B29" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="137">
+      <c r="C29" s="132">
         <f>B10*C10</f>
         <v>0</v>
       </c>
-      <c r="D29" s="137">
+      <c r="D29" s="132">
         <f>B10*D10</f>
         <v>0</v>
       </c>
-      <c r="E29" s="137">
+      <c r="E29" s="132">
         <f>B10*E10</f>
         <v>0</v>
       </c>
-      <c r="F29" s="137">
+      <c r="F29" s="132">
         <f>B10*F10</f>
         <v>0</v>
       </c>
-      <c r="G29" s="137">
+      <c r="G29" s="132">
         <f>B10*G10</f>
         <v>0</v>
       </c>
-      <c r="H29" s="137">
+      <c r="H29" s="132">
         <f>B10*H10</f>
         <v>0</v>
       </c>
-      <c r="I29" s="137">
+      <c r="I29" s="132">
         <f>B10*I10</f>
         <v>0</v>
       </c>
-      <c r="J29" s="137">
+      <c r="J29" s="132">
         <f>SUM(C29:I29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="141" t="s">
+      <c r="A30" s="136" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="141"/>
-      <c r="C30" s="139">
+      <c r="B30" s="136"/>
+      <c r="C30" s="134">
         <f>SUM(C25:C29)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="139">
+      <c r="D30" s="134">
         <f t="shared" ref="D30:J30" si="4">SUM(D25:D29)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="139">
+      <c r="E30" s="134">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F30" s="139">
+      <c r="F30" s="134">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G30" s="139">
+      <c r="G30" s="134">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H30" s="139">
+      <c r="H30" s="134">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I30" s="139">
+      <c r="I30" s="134">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="139">
+      <c r="J30" s="134">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="140" t="s">
+      <c r="A31" s="135" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="131" t="s">
+      <c r="B31" s="126" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="137"/>
-      <c r="D31" s="137"/>
-      <c r="E31" s="137"/>
-      <c r="F31" s="137"/>
-      <c r="G31" s="137"/>
-      <c r="H31" s="137"/>
-      <c r="I31" s="137"/>
-      <c r="J31" s="132">
+      <c r="C31" s="132"/>
+      <c r="D31" s="132"/>
+      <c r="E31" s="132"/>
+      <c r="F31" s="132"/>
+      <c r="G31" s="132"/>
+      <c r="H31" s="132"/>
+      <c r="I31" s="132"/>
+      <c r="J31" s="127">
         <f>SUM(C31:I31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="140" t="s">
+      <c r="A32" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="131" t="s">
+      <c r="B32" s="126" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="137"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="137"/>
-      <c r="H32" s="137"/>
-      <c r="I32" s="137"/>
-      <c r="J32" s="132">
+      <c r="C32" s="132"/>
+      <c r="D32" s="132"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="132"/>
+      <c r="G32" s="132"/>
+      <c r="H32" s="132"/>
+      <c r="I32" s="132"/>
+      <c r="J32" s="127">
         <f t="shared" ref="J32:J41" si="5">SUM(C32:I32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="140" t="s">
+      <c r="A33" s="135" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="131" t="s">
+      <c r="B33" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="137"/>
-      <c r="D33" s="137"/>
-      <c r="E33" s="137"/>
-      <c r="F33" s="137"/>
-      <c r="G33" s="137"/>
-      <c r="H33" s="137"/>
-      <c r="I33" s="137"/>
-      <c r="J33" s="132">
+      <c r="C33" s="132"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="132"/>
+      <c r="J33" s="127">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="140" t="s">
+      <c r="A34" s="135" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="131" t="s">
+      <c r="B34" s="126" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="137"/>
-      <c r="D34" s="137"/>
-      <c r="E34" s="137"/>
-      <c r="F34" s="137"/>
-      <c r="G34" s="137"/>
-      <c r="H34" s="137"/>
-      <c r="I34" s="137"/>
-      <c r="J34" s="132">
+      <c r="C34" s="132"/>
+      <c r="D34" s="132"/>
+      <c r="E34" s="132"/>
+      <c r="F34" s="132"/>
+      <c r="G34" s="132"/>
+      <c r="H34" s="132"/>
+      <c r="I34" s="132"/>
+      <c r="J34" s="127">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="142" t="s">
+      <c r="A35" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="B35" s="142"/>
-      <c r="C35" s="139">
+      <c r="B35" s="137"/>
+      <c r="C35" s="134">
         <f>SUM(C31:C34)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="139">
+      <c r="D35" s="134">
         <f t="shared" ref="D35:I35" si="6">SUM(D31:D34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="139">
+      <c r="E35" s="134">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F35" s="139">
+      <c r="F35" s="134">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G35" s="139">
+      <c r="G35" s="134">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H35" s="139">
+      <c r="H35" s="134">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I35" s="139">
+      <c r="I35" s="134">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J35" s="134">
+      <c r="J35" s="129">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="140" t="s">
+      <c r="A36" s="135" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="131" t="s">
+      <c r="B36" s="126" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="137"/>
-      <c r="D36" s="132"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="143"/>
-      <c r="H36" s="143"/>
-      <c r="I36" s="143"/>
-      <c r="J36" s="132">
+      <c r="C36" s="132"/>
+      <c r="D36" s="127"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="132"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
+      <c r="J36" s="127">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="140" t="s">
+      <c r="A37" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="131" t="s">
+      <c r="B37" s="126" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="137"/>
-      <c r="D37" s="132"/>
-      <c r="E37" s="137"/>
-      <c r="F37" s="137"/>
-      <c r="G37" s="143"/>
-      <c r="H37" s="143"/>
-      <c r="I37" s="143"/>
-      <c r="J37" s="132">
+      <c r="C37" s="132"/>
+      <c r="D37" s="127"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="132"/>
+      <c r="G37" s="138"/>
+      <c r="H37" s="138"/>
+      <c r="I37" s="138"/>
+      <c r="J37" s="127">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="140" t="s">
+      <c r="A38" s="135" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="131" t="s">
+      <c r="B38" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="137"/>
-      <c r="D38" s="132"/>
-      <c r="E38" s="137"/>
-      <c r="F38" s="137"/>
-      <c r="G38" s="143"/>
-      <c r="H38" s="143"/>
-      <c r="I38" s="143"/>
-      <c r="J38" s="132">
+      <c r="C38" s="132"/>
+      <c r="D38" s="127"/>
+      <c r="E38" s="132"/>
+      <c r="F38" s="132"/>
+      <c r="G38" s="138"/>
+      <c r="H38" s="138"/>
+      <c r="I38" s="138"/>
+      <c r="J38" s="127">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="140" t="s">
+      <c r="A39" s="135" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="131" t="s">
+      <c r="B39" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="137"/>
-      <c r="D39" s="132"/>
-      <c r="E39" s="137"/>
-      <c r="F39" s="137"/>
-      <c r="G39" s="143"/>
-      <c r="H39" s="143"/>
-      <c r="I39" s="143"/>
-      <c r="J39" s="132">
+      <c r="C39" s="132"/>
+      <c r="D39" s="127"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="138"/>
+      <c r="H39" s="138"/>
+      <c r="I39" s="138"/>
+      <c r="J39" s="127">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="144" t="s">
+      <c r="A40" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="131" t="s">
+      <c r="B40" s="126" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="137"/>
-      <c r="D40" s="132"/>
-      <c r="E40" s="137"/>
-      <c r="F40" s="137"/>
-      <c r="G40" s="143"/>
-      <c r="H40" s="143"/>
-      <c r="I40" s="143"/>
-      <c r="J40" s="132">
+      <c r="C40" s="132"/>
+      <c r="D40" s="127"/>
+      <c r="E40" s="132"/>
+      <c r="F40" s="132"/>
+      <c r="G40" s="138"/>
+      <c r="H40" s="138"/>
+      <c r="I40" s="138"/>
+      <c r="J40" s="127">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="141" t="s">
+      <c r="A41" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="141"/>
-      <c r="C41" s="139">
+      <c r="B41" s="136"/>
+      <c r="C41" s="134">
         <f>SUM(C17,C24,C30,C35,C36:C40)-C17</f>
         <v>0</v>
       </c>
-      <c r="D41" s="139">
+      <c r="D41" s="134">
         <f t="shared" ref="D41:I41" si="7">SUM(D17,D24,D30,D35,D36:D40)-D17</f>
         <v>0</v>
       </c>
-      <c r="E41" s="139">
+      <c r="E41" s="134">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F41" s="139">
+      <c r="F41" s="134">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G41" s="139">
+      <c r="G41" s="134">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H41" s="139">
+      <c r="H41" s="134">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I41" s="139">
+      <c r="I41" s="134">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J41" s="134">
+      <c r="J41" s="129">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="140" t="s">
+      <c r="A42" s="135" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="145" t="s">
+      <c r="B42" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="137"/>
-      <c r="D42" s="137"/>
-      <c r="E42" s="137"/>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
-      <c r="H42" s="137"/>
-      <c r="I42" s="137"/>
-      <c r="J42" s="132">
+      <c r="C42" s="132"/>
+      <c r="D42" s="132"/>
+      <c r="E42" s="132"/>
+      <c r="F42" s="132"/>
+      <c r="G42" s="132"/>
+      <c r="H42" s="132"/>
+      <c r="I42" s="132"/>
+      <c r="J42" s="127">
         <f>SUM(C42:I42)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="140" t="s">
+      <c r="A43" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="145" t="s">
+      <c r="B43" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="C43" s="137"/>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137"/>
-      <c r="F43" s="137"/>
-      <c r="G43" s="137"/>
-      <c r="H43" s="137"/>
-      <c r="I43" s="137"/>
-      <c r="J43" s="132">
+      <c r="C43" s="132"/>
+      <c r="D43" s="132"/>
+      <c r="E43" s="132"/>
+      <c r="F43" s="132"/>
+      <c r="G43" s="132"/>
+      <c r="H43" s="132"/>
+      <c r="I43" s="132"/>
+      <c r="J43" s="127">
         <f t="shared" ref="J43:J50" si="8">SUM(C43:I43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="140" t="s">
+      <c r="A44" s="135" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="145" t="s">
+      <c r="B44" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="137"/>
-      <c r="D44" s="137"/>
-      <c r="E44" s="137"/>
-      <c r="F44" s="137"/>
-      <c r="G44" s="137"/>
-      <c r="H44" s="137"/>
-      <c r="I44" s="137"/>
-      <c r="J44" s="132">
+      <c r="C44" s="132"/>
+      <c r="D44" s="132"/>
+      <c r="E44" s="132"/>
+      <c r="F44" s="132"/>
+      <c r="G44" s="132"/>
+      <c r="H44" s="132"/>
+      <c r="I44" s="132"/>
+      <c r="J44" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="146" t="s">
+      <c r="A45" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="140"/>
-      <c r="C45" s="139">
+      <c r="B45" s="135"/>
+      <c r="C45" s="134">
         <f>SUM(C42:C44)</f>
         <v>0</v>
       </c>
-      <c r="D45" s="139">
+      <c r="D45" s="134">
         <f t="shared" ref="D45:I45" si="9">SUM(D42:D44)</f>
         <v>0</v>
       </c>
-      <c r="E45" s="139">
+      <c r="E45" s="134">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F45" s="139">
+      <c r="F45" s="134">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G45" s="139">
+      <c r="G45" s="134">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H45" s="139">
+      <c r="H45" s="134">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I45" s="139">
+      <c r="I45" s="134">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J45" s="134">
+      <c r="J45" s="129">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="140" t="s">
+      <c r="A46" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="B46" s="145" t="s">
+      <c r="B46" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="137"/>
-      <c r="D46" s="137"/>
-      <c r="E46" s="137"/>
-      <c r="F46" s="137"/>
-      <c r="G46" s="137"/>
-      <c r="H46" s="137"/>
-      <c r="I46" s="137"/>
-      <c r="J46" s="132">
+      <c r="C46" s="132"/>
+      <c r="D46" s="132"/>
+      <c r="E46" s="132"/>
+      <c r="F46" s="132"/>
+      <c r="G46" s="132"/>
+      <c r="H46" s="132"/>
+      <c r="I46" s="132"/>
+      <c r="J46" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="140" t="s">
+      <c r="A47" s="135" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="145" t="s">
+      <c r="B47" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="C47" s="137"/>
-      <c r="D47" s="137"/>
-      <c r="E47" s="137"/>
-      <c r="F47" s="137"/>
-      <c r="G47" s="137"/>
-      <c r="H47" s="137"/>
-      <c r="I47" s="137"/>
-      <c r="J47" s="132">
+      <c r="C47" s="132"/>
+      <c r="D47" s="132"/>
+      <c r="E47" s="132"/>
+      <c r="F47" s="132"/>
+      <c r="G47" s="132"/>
+      <c r="H47" s="132"/>
+      <c r="I47" s="132"/>
+      <c r="J47" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="140" t="s">
+      <c r="A48" s="135" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="145" t="s">
+      <c r="B48" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="C48" s="137"/>
-      <c r="D48" s="137"/>
-      <c r="E48" s="137"/>
-      <c r="F48" s="137"/>
-      <c r="G48" s="137"/>
-      <c r="H48" s="137"/>
-      <c r="I48" s="137"/>
-      <c r="J48" s="132">
+      <c r="C48" s="132"/>
+      <c r="D48" s="132"/>
+      <c r="E48" s="132"/>
+      <c r="F48" s="132"/>
+      <c r="G48" s="132"/>
+      <c r="H48" s="132"/>
+      <c r="I48" s="132"/>
+      <c r="J48" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="140" t="s">
+      <c r="A49" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="145" t="s">
+      <c r="B49" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="137"/>
-      <c r="D49" s="137"/>
-      <c r="E49" s="137"/>
-      <c r="F49" s="137"/>
-      <c r="G49" s="137"/>
-      <c r="H49" s="137"/>
-      <c r="I49" s="137"/>
-      <c r="J49" s="132">
+      <c r="C49" s="132"/>
+      <c r="D49" s="132"/>
+      <c r="E49" s="132"/>
+      <c r="F49" s="132"/>
+      <c r="G49" s="132"/>
+      <c r="H49" s="132"/>
+      <c r="I49" s="132"/>
+      <c r="J49" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="146" t="s">
+      <c r="A50" s="141" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="140"/>
-      <c r="C50" s="139">
+      <c r="B50" s="135"/>
+      <c r="C50" s="134">
         <f>SUM(C46:C49)</f>
         <v>0</v>
       </c>
-      <c r="D50" s="139">
+      <c r="D50" s="134">
         <f t="shared" ref="D50:I50" si="10">SUM(D46:D49)</f>
         <v>0</v>
       </c>
-      <c r="E50" s="139">
+      <c r="E50" s="134">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F50" s="139">
+      <c r="F50" s="134">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G50" s="139">
+      <c r="G50" s="134">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H50" s="139">
+      <c r="H50" s="134">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I50" s="139">
+      <c r="I50" s="134">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J50" s="134">
+      <c r="J50" s="129">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="147"/>
-      <c r="B51" s="148"/>
-      <c r="C51" s="137"/>
-      <c r="D51" s="137"/>
-      <c r="E51" s="137"/>
-      <c r="F51" s="137"/>
-      <c r="G51" s="137"/>
-      <c r="H51" s="137"/>
-      <c r="I51" s="137"/>
-      <c r="J51" s="132"/>
+      <c r="A51" s="42"/>
+      <c r="B51" s="142"/>
+      <c r="C51" s="132"/>
+      <c r="D51" s="132"/>
+      <c r="E51" s="132"/>
+      <c r="F51" s="132"/>
+      <c r="G51" s="132"/>
+      <c r="H51" s="132"/>
+      <c r="I51" s="132"/>
+      <c r="J51" s="127"/>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="141" t="s">
+      <c r="A52" s="136" t="s">
         <v>82</v>
       </c>
-      <c r="B52" s="141"/>
-      <c r="C52" s="139">
+      <c r="B52" s="136"/>
+      <c r="C52" s="134">
         <f>SUM(C41,C45,C50)</f>
         <v>0</v>
       </c>
-      <c r="D52" s="139">
+      <c r="D52" s="134">
         <f t="shared" ref="D52:I52" si="11">SUM(D41,D45,D50)</f>
         <v>0</v>
       </c>
-      <c r="E52" s="139">
+      <c r="E52" s="134">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F52" s="139">
+      <c r="F52" s="134">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G52" s="139">
+      <c r="G52" s="134">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H52" s="139">
+      <c r="H52" s="134">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I52" s="139">
+      <c r="I52" s="134">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J52" s="139">
+      <c r="J52" s="134">
         <f>SUM(C52:I52)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C53" s="149"/>
-      <c r="D53" s="150"/>
-      <c r="E53" s="149"/>
-      <c r="F53" s="149"/>
-      <c r="G53" s="150"/>
-      <c r="H53" s="150"/>
-      <c r="I53" s="150"/>
-      <c r="J53" s="151"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="13"/>
     </row>
     <row r="54" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="152" t="s">
+      <c r="A54" s="143" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="153"/>
-      <c r="C54" s="154"/>
-      <c r="D54" s="155" t="s">
+      <c r="B54" s="144"/>
+      <c r="C54" s="145"/>
+      <c r="D54" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="E54" s="156" t="s">
+      <c r="E54" s="147" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="157"/>
-      <c r="G54" s="157"/>
-      <c r="H54" s="158"/>
-      <c r="I54" s="159" t="s">
+      <c r="F54" s="148"/>
+      <c r="G54" s="148"/>
+      <c r="H54" s="149"/>
+      <c r="I54" s="150" t="s">
         <v>67</v>
       </c>
-      <c r="J54" s="160">
+      <c r="J54" s="151">
         <f>J52</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="161"/>
-      <c r="B55" s="162"/>
-      <c r="C55" s="163"/>
-      <c r="D55" s="164"/>
-      <c r="E55" s="165"/>
-      <c r="F55" s="166"/>
-      <c r="G55" s="166"/>
-      <c r="H55" s="167"/>
-      <c r="I55" s="168" t="s">
+      <c r="A55" s="152"/>
+      <c r="B55" s="153"/>
+      <c r="C55" s="154"/>
+      <c r="D55" s="155"/>
+      <c r="E55" s="156"/>
+      <c r="F55" s="157"/>
+      <c r="G55" s="157"/>
+      <c r="H55" s="80"/>
+      <c r="I55" s="158" t="s">
         <v>66</v>
       </c>
-      <c r="J55" s="169"/>
+      <c r="J55" s="159"/>
     </row>
     <row r="56" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="152" t="s">
+      <c r="A56" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="B56" s="153"/>
-      <c r="C56" s="154"/>
-      <c r="D56" s="170" t="s">
+      <c r="B56" s="144"/>
+      <c r="C56" s="145"/>
+      <c r="D56" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="E56" s="171" t="s">
+      <c r="E56" s="161" t="s">
         <v>54</v>
       </c>
-      <c r="F56" s="172"/>
-      <c r="G56" s="173"/>
-      <c r="H56" s="170" t="s">
+      <c r="F56" s="10"/>
+      <c r="G56" s="162"/>
+      <c r="H56" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="I56" s="174"/>
-      <c r="J56" s="169"/>
+      <c r="I56" s="163"/>
+      <c r="J56" s="159"/>
     </row>
     <row r="57" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="161"/>
-      <c r="B57" s="162"/>
-      <c r="C57" s="163"/>
-      <c r="D57" s="175"/>
-      <c r="E57" s="176"/>
-      <c r="F57" s="177"/>
-      <c r="G57" s="163"/>
-      <c r="H57" s="178"/>
-      <c r="I57" s="179"/>
-      <c r="J57" s="180"/>
+      <c r="A57" s="152"/>
+      <c r="B57" s="153"/>
+      <c r="C57" s="154"/>
+      <c r="D57" s="164"/>
+      <c r="E57" s="165"/>
+      <c r="F57" s="166"/>
+      <c r="G57" s="154"/>
+      <c r="H57" s="167"/>
+      <c r="I57" s="168"/>
+      <c r="J57" s="169"/>
     </row>
   </sheetData>
   <mergeCells count="17">

--- a/Expenses Form.xlsx
+++ b/Expenses Form.xlsx
@@ -474,7 +474,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -483,71 +483,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -560,58 +505,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -638,30 +531,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -682,24 +551,15 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -713,19 +573,132 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1132,269 +1105,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf applyBorder="1" numFmtId="2" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1948,1050 +1658,1050 @@
       <c r="J4" s="68"/>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="105"/>
+      <c r="B5" s="4"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="112"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="71"/>
     </row>
     <row r="6" spans="1:10" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="114"/>
-      <c r="C6" s="115" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="115" t="s">
+      <c r="D6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="116" t="s">
+      <c r="E6" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="115" t="s">
+      <c r="F6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="115" t="s">
+      <c r="G6" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="116" t="s">
+      <c r="H6" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="116" t="s">
+      <c r="I6" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="116" t="s">
+      <c r="J6" s="58" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="114" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="114"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="118"/>
+      <c r="A7" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="64"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="16"/>
     </row>
     <row r="8" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="114" t="s">
+      <c r="A8" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="114"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="117"/>
-      <c r="J8" s="118"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="119" t="s">
+      <c r="A9" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="118"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="16"/>
     </row>
     <row r="10" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="121">
+      <c r="B10" s="41">
         <v>0.7</v>
       </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="122"/>
-      <c r="H10" s="122"/>
-      <c r="I10" s="122"/>
-      <c r="J10" s="118"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="16"/>
     </row>
     <row r="11" spans="1:10" s="8" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="60"/>
-      <c r="B11" s="123"/>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="124"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="62"/>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="125" t="s">
+      <c r="A12" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="126"/>
-      <c r="C12" s="127"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="127">
+      <c r="B12" s="28"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19">
         <f t="shared" ref="J12:J17" si="0">SUM(C12:I12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="125" t="s">
+      <c r="A13" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="125"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127">
+      <c r="B13" s="11"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="125" t="s">
+      <c r="A14" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="125"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127">
+      <c r="B14" s="11"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="127">
+      <c r="B15" s="11"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="125" t="s">
+      <c r="A16" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="125"/>
-      <c r="C16" s="127"/>
-      <c r="D16" s="127"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="127">
+      <c r="B16" s="11"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="128" t="s">
+      <c r="A17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="128"/>
-      <c r="C17" s="129">
+      <c r="B17" s="12"/>
+      <c r="C17" s="26">
         <f>SUM(C12:C16)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="129">
+      <c r="D17" s="26">
         <f t="shared" ref="D17:I17" si="1">SUM(D12:D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="129">
+      <c r="E17" s="26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F17" s="129">
+      <c r="F17" s="26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="129">
+      <c r="G17" s="26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H17" s="129">
+      <c r="H17" s="26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I17" s="129">
+      <c r="I17" s="26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="129">
+      <c r="J17" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="130" t="s">
+      <c r="A18" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="131" t="s">
+      <c r="B18" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="132"/>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="132"/>
-      <c r="I18" s="132"/>
-      <c r="J18" s="132">
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24">
         <f t="shared" ref="J18:J23" si="2">SUM(C18:I18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="130" t="s">
+      <c r="A19" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="131" t="s">
+      <c r="B19" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="132"/>
-      <c r="D19" s="132"/>
-      <c r="E19" s="132"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="132"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="132"/>
-      <c r="J19" s="132">
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="130" t="s">
+      <c r="A20" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="131" t="s">
+      <c r="B20" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="132"/>
-      <c r="D20" s="132"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="132"/>
-      <c r="G20" s="132"/>
-      <c r="H20" s="132"/>
-      <c r="I20" s="132"/>
-      <c r="J20" s="132">
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="130" t="s">
+      <c r="A21" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="131" t="s">
+      <c r="B21" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="132"/>
-      <c r="D21" s="132"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="132"/>
-      <c r="J21" s="132">
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="130" t="s">
+      <c r="A22" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="131" t="s">
+      <c r="B22" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="132"/>
-      <c r="D22" s="132"/>
-      <c r="E22" s="132"/>
-      <c r="F22" s="132"/>
-      <c r="G22" s="132"/>
-      <c r="H22" s="132"/>
-      <c r="I22" s="132"/>
-      <c r="J22" s="132">
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="130" t="s">
+      <c r="A23" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="131" t="s">
+      <c r="B23" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="132"/>
-      <c r="D23" s="132"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="132"/>
-      <c r="I23" s="132"/>
-      <c r="J23" s="132">
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="133" t="s">
+      <c r="A24" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="133"/>
-      <c r="C24" s="134">
+      <c r="B24" s="84"/>
+      <c r="C24" s="25">
         <f>SUM(C18:C23)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="134">
+      <c r="D24" s="25">
         <f t="shared" ref="D24:J24" si="3">SUM(D18:D23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="134">
+      <c r="E24" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F24" s="134">
+      <c r="F24" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G24" s="134">
+      <c r="G24" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H24" s="134">
+      <c r="H24" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I24" s="134">
+      <c r="I24" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="134">
+      <c r="J24" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="135" t="s">
+      <c r="A25" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="126" t="s">
+      <c r="B25" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="132"/>
-      <c r="D25" s="132"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="132"/>
-      <c r="J25" s="132">
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24">
         <f>SUM(C25:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="135" t="s">
+      <c r="A26" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="126" t="s">
+      <c r="B26" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="132"/>
-      <c r="D26" s="132"/>
-      <c r="E26" s="132"/>
-      <c r="F26" s="132"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="132"/>
-      <c r="I26" s="132"/>
-      <c r="J26" s="132">
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24">
         <f>SUM(C26:I26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="135" t="s">
+      <c r="A27" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="126" t="s">
+      <c r="B27" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="132"/>
-      <c r="D27" s="132"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="132"/>
-      <c r="J27" s="132">
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24">
         <f>SUM(C27:I27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="135" t="s">
+      <c r="A28" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="126" t="s">
+      <c r="B28" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="132"/>
-      <c r="D28" s="132"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="132"/>
-      <c r="H28" s="132"/>
-      <c r="I28" s="132"/>
-      <c r="J28" s="132">
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24">
         <f>SUM(C28:I28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="135" t="s">
+      <c r="A29" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="126" t="s">
+      <c r="B29" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="132">
+      <c r="C29" s="24">
         <f>B10*C10</f>
         <v>0</v>
       </c>
-      <c r="D29" s="132">
+      <c r="D29" s="24">
         <f>B10*D10</f>
         <v>0</v>
       </c>
-      <c r="E29" s="132">
+      <c r="E29" s="24">
         <f>B10*E10</f>
         <v>0</v>
       </c>
-      <c r="F29" s="132">
+      <c r="F29" s="24">
         <f>B10*F10</f>
         <v>0</v>
       </c>
-      <c r="G29" s="132">
+      <c r="G29" s="24">
         <f>B10*G10</f>
         <v>0</v>
       </c>
-      <c r="H29" s="132">
+      <c r="H29" s="24">
         <f>B10*H10</f>
         <v>0</v>
       </c>
-      <c r="I29" s="132">
+      <c r="I29" s="24">
         <f>B10*I10</f>
         <v>0</v>
       </c>
-      <c r="J29" s="132">
+      <c r="J29" s="24">
         <f>SUM(C29:I29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="136" t="s">
+      <c r="A30" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="136"/>
-      <c r="C30" s="134">
+      <c r="B30" s="85"/>
+      <c r="C30" s="25">
         <f>SUM(C25:C29)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="134">
+      <c r="D30" s="25">
         <f t="shared" ref="D30:J30" si="4">SUM(D25:D29)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="134">
+      <c r="E30" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F30" s="134">
+      <c r="F30" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G30" s="134">
+      <c r="G30" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H30" s="134">
+      <c r="H30" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I30" s="134">
+      <c r="I30" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="134">
+      <c r="J30" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="135" t="s">
+      <c r="A31" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="126" t="s">
+      <c r="B31" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="132"/>
-      <c r="D31" s="132"/>
-      <c r="E31" s="132"/>
-      <c r="F31" s="132"/>
-      <c r="G31" s="132"/>
-      <c r="H31" s="132"/>
-      <c r="I31" s="132"/>
-      <c r="J31" s="127">
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="19">
         <f>SUM(C31:I31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="126" t="s">
+      <c r="B32" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="132"/>
-      <c r="D32" s="132"/>
-      <c r="E32" s="132"/>
-      <c r="F32" s="132"/>
-      <c r="G32" s="132"/>
-      <c r="H32" s="132"/>
-      <c r="I32" s="132"/>
-      <c r="J32" s="127">
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="19">
         <f t="shared" ref="J32:J41" si="5">SUM(C32:I32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="135" t="s">
+      <c r="A33" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="126" t="s">
+      <c r="B33" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="132"/>
-      <c r="D33" s="132"/>
-      <c r="E33" s="132"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="132"/>
-      <c r="H33" s="132"/>
-      <c r="I33" s="132"/>
-      <c r="J33" s="127">
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="135" t="s">
+      <c r="A34" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="126" t="s">
+      <c r="B34" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="132"/>
-      <c r="D34" s="132"/>
-      <c r="E34" s="132"/>
-      <c r="F34" s="132"/>
-      <c r="G34" s="132"/>
-      <c r="H34" s="132"/>
-      <c r="I34" s="132"/>
-      <c r="J34" s="127">
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="137" t="s">
+      <c r="A35" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="B35" s="137"/>
-      <c r="C35" s="134">
+      <c r="B35" s="86"/>
+      <c r="C35" s="25">
         <f>SUM(C31:C34)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="134">
+      <c r="D35" s="25">
         <f t="shared" ref="D35:I35" si="6">SUM(D31:D34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="134">
+      <c r="E35" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F35" s="134">
+      <c r="F35" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G35" s="134">
+      <c r="G35" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H35" s="134">
+      <c r="H35" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I35" s="134">
+      <c r="I35" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J35" s="129">
+      <c r="J35" s="26">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="135" t="s">
+      <c r="A36" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="126" t="s">
+      <c r="B36" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="132"/>
-      <c r="D36" s="127"/>
-      <c r="E36" s="132"/>
-      <c r="F36" s="132"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="127">
+      <c r="C36" s="24"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="135" t="s">
+      <c r="A37" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="126" t="s">
+      <c r="B37" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="132"/>
-      <c r="D37" s="127"/>
-      <c r="E37" s="132"/>
-      <c r="F37" s="132"/>
-      <c r="G37" s="138"/>
-      <c r="H37" s="138"/>
-      <c r="I37" s="138"/>
-      <c r="J37" s="127">
+      <c r="C37" s="24"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="135" t="s">
+      <c r="A38" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="126" t="s">
+      <c r="B38" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="132"/>
-      <c r="D38" s="127"/>
-      <c r="E38" s="132"/>
-      <c r="F38" s="132"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="127">
+      <c r="C38" s="24"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="135" t="s">
+      <c r="A39" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="126" t="s">
+      <c r="B39" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="132"/>
-      <c r="D39" s="127"/>
-      <c r="E39" s="132"/>
-      <c r="F39" s="132"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="138"/>
-      <c r="I39" s="138"/>
-      <c r="J39" s="127">
+      <c r="C39" s="24"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="139" t="s">
+      <c r="A40" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="126" t="s">
+      <c r="B40" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="132"/>
-      <c r="D40" s="127"/>
-      <c r="E40" s="132"/>
-      <c r="F40" s="132"/>
-      <c r="G40" s="138"/>
-      <c r="H40" s="138"/>
-      <c r="I40" s="138"/>
-      <c r="J40" s="127">
+      <c r="C40" s="24"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="136" t="s">
+      <c r="A41" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="136"/>
-      <c r="C41" s="134">
+      <c r="B41" s="85"/>
+      <c r="C41" s="25">
         <f>SUM(C17,C24,C30,C35,C36:C40)-C17</f>
         <v>0</v>
       </c>
-      <c r="D41" s="134">
+      <c r="D41" s="25">
         <f t="shared" ref="D41:I41" si="7">SUM(D17,D24,D30,D35,D36:D40)-D17</f>
         <v>0</v>
       </c>
-      <c r="E41" s="134">
+      <c r="E41" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F41" s="134">
+      <c r="F41" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G41" s="134">
+      <c r="G41" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H41" s="134">
+      <c r="H41" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I41" s="134">
+      <c r="I41" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J41" s="129">
+      <c r="J41" s="26">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="135" t="s">
+      <c r="A42" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="140" t="s">
+      <c r="B42" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="132"/>
-      <c r="D42" s="132"/>
-      <c r="E42" s="132"/>
-      <c r="F42" s="132"/>
-      <c r="G42" s="132"/>
-      <c r="H42" s="132"/>
-      <c r="I42" s="132"/>
-      <c r="J42" s="127">
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="19">
         <f>SUM(C42:I42)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="135" t="s">
+      <c r="A43" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="140" t="s">
+      <c r="B43" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C43" s="132"/>
-      <c r="D43" s="132"/>
-      <c r="E43" s="132"/>
-      <c r="F43" s="132"/>
-      <c r="G43" s="132"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
-      <c r="J43" s="127">
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="19">
         <f t="shared" ref="J43:J50" si="8">SUM(C43:I43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="135" t="s">
+      <c r="A44" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="140" t="s">
+      <c r="B44" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="132"/>
-      <c r="D44" s="132"/>
-      <c r="E44" s="132"/>
-      <c r="F44" s="132"/>
-      <c r="G44" s="132"/>
-      <c r="H44" s="132"/>
-      <c r="I44" s="132"/>
-      <c r="J44" s="127">
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="19">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="141" t="s">
+      <c r="A45" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="135"/>
-      <c r="C45" s="134">
+      <c r="B45" s="21"/>
+      <c r="C45" s="25">
         <f>SUM(C42:C44)</f>
         <v>0</v>
       </c>
-      <c r="D45" s="134">
+      <c r="D45" s="25">
         <f t="shared" ref="D45:I45" si="9">SUM(D42:D44)</f>
         <v>0</v>
       </c>
-      <c r="E45" s="134">
+      <c r="E45" s="25">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F45" s="134">
+      <c r="F45" s="25">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G45" s="134">
+      <c r="G45" s="25">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H45" s="134">
+      <c r="H45" s="25">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I45" s="134">
+      <c r="I45" s="25">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J45" s="129">
+      <c r="J45" s="26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="135" t="s">
+      <c r="A46" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="B46" s="140" t="s">
+      <c r="B46" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="132"/>
-      <c r="D46" s="132"/>
-      <c r="E46" s="132"/>
-      <c r="F46" s="132"/>
-      <c r="G46" s="132"/>
-      <c r="H46" s="132"/>
-      <c r="I46" s="132"/>
-      <c r="J46" s="127">
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="19">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="135" t="s">
+      <c r="A47" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="140" t="s">
+      <c r="B47" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C47" s="132"/>
-      <c r="D47" s="132"/>
-      <c r="E47" s="132"/>
-      <c r="F47" s="132"/>
-      <c r="G47" s="132"/>
-      <c r="H47" s="132"/>
-      <c r="I47" s="132"/>
-      <c r="J47" s="127">
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="19">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="135" t="s">
+      <c r="A48" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="140" t="s">
+      <c r="B48" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C48" s="132"/>
-      <c r="D48" s="132"/>
-      <c r="E48" s="132"/>
-      <c r="F48" s="132"/>
-      <c r="G48" s="132"/>
-      <c r="H48" s="132"/>
-      <c r="I48" s="132"/>
-      <c r="J48" s="127">
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="19">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="135" t="s">
+      <c r="A49" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="140" t="s">
+      <c r="B49" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="132"/>
-      <c r="D49" s="132"/>
-      <c r="E49" s="132"/>
-      <c r="F49" s="132"/>
-      <c r="G49" s="132"/>
-      <c r="H49" s="132"/>
-      <c r="I49" s="132"/>
-      <c r="J49" s="127">
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="19">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="141" t="s">
+      <c r="A50" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="135"/>
-      <c r="C50" s="134">
+      <c r="B50" s="21"/>
+      <c r="C50" s="25">
         <f>SUM(C46:C49)</f>
         <v>0</v>
       </c>
-      <c r="D50" s="134">
+      <c r="D50" s="25">
         <f t="shared" ref="D50:I50" si="10">SUM(D46:D49)</f>
         <v>0</v>
       </c>
-      <c r="E50" s="134">
+      <c r="E50" s="25">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F50" s="134">
+      <c r="F50" s="25">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G50" s="134">
+      <c r="G50" s="25">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H50" s="134">
+      <c r="H50" s="25">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I50" s="134">
+      <c r="I50" s="25">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J50" s="129">
+      <c r="J50" s="26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="42"/>
-      <c r="B51" s="142"/>
-      <c r="C51" s="132"/>
-      <c r="D51" s="132"/>
-      <c r="E51" s="132"/>
-      <c r="F51" s="132"/>
-      <c r="G51" s="132"/>
-      <c r="H51" s="132"/>
-      <c r="I51" s="132"/>
-      <c r="J51" s="127"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="19"/>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="136" t="s">
+      <c r="A52" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="B52" s="136"/>
-      <c r="C52" s="134">
+      <c r="B52" s="85"/>
+      <c r="C52" s="25">
         <f>SUM(C41,C45,C50)</f>
         <v>0</v>
       </c>
-      <c r="D52" s="134">
+      <c r="D52" s="25">
         <f t="shared" ref="D52:I52" si="11">SUM(D41,D45,D50)</f>
         <v>0</v>
       </c>
-      <c r="E52" s="134">
+      <c r="E52" s="25">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F52" s="134">
+      <c r="F52" s="25">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G52" s="134">
+      <c r="G52" s="25">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H52" s="134">
+      <c r="H52" s="25">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I52" s="134">
+      <c r="I52" s="25">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J52" s="134">
+      <c r="J52" s="25">
         <f>SUM(C52:I52)</f>
         <v>0</v>
       </c>
@@ -3007,73 +2717,73 @@
       <c r="J53" s="13"/>
     </row>
     <row r="54" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="143" t="s">
+      <c r="A54" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="144"/>
-      <c r="C54" s="145"/>
-      <c r="D54" s="146" t="s">
+      <c r="B54" s="30"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E54" s="147" t="s">
+      <c r="E54" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="148"/>
-      <c r="G54" s="148"/>
-      <c r="H54" s="149"/>
-      <c r="I54" s="150" t="s">
+      <c r="F54" s="76"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="77"/>
+      <c r="I54" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="J54" s="151">
+      <c r="J54" s="72">
         <f>J52</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="152"/>
-      <c r="B55" s="153"/>
-      <c r="C55" s="154"/>
-      <c r="D55" s="155"/>
-      <c r="E55" s="156"/>
-      <c r="F55" s="157"/>
-      <c r="G55" s="157"/>
+      <c r="A55" s="32"/>
+      <c r="B55" s="33"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="78"/>
+      <c r="F55" s="79"/>
+      <c r="G55" s="79"/>
       <c r="H55" s="80"/>
-      <c r="I55" s="158" t="s">
+      <c r="I55" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="J55" s="159"/>
+      <c r="J55" s="73"/>
     </row>
     <row r="56" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="143" t="s">
+      <c r="A56" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B56" s="144"/>
-      <c r="C56" s="145"/>
-      <c r="D56" s="160" t="s">
+      <c r="B56" s="30"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E56" s="161" t="s">
+      <c r="E56" s="40" t="s">
         <v>54</v>
       </c>
       <c r="F56" s="10"/>
-      <c r="G56" s="162"/>
-      <c r="H56" s="160" t="s">
+      <c r="G56" s="10"/>
+      <c r="H56" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I56" s="163"/>
-      <c r="J56" s="159"/>
+      <c r="I56" s="82"/>
+      <c r="J56" s="73"/>
     </row>
     <row r="57" spans="1:10" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="152"/>
-      <c r="B57" s="153"/>
-      <c r="C57" s="154"/>
-      <c r="D57" s="164"/>
-      <c r="E57" s="165"/>
-      <c r="F57" s="166"/>
-      <c r="G57" s="154"/>
-      <c r="H57" s="167"/>
-      <c r="I57" s="168"/>
-      <c r="J57" s="169"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="83"/>
+      <c r="J57" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="17">
